--- a/subjects.xlsx
+++ b/subjects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/JBooth-Lab/BDL/Marjolein/Morph_7/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Marjo/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2516404C-CEEE-124D-9ACB-34F478176B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C57A85-D267-584C-BF37-8C2144102060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="17780" windowHeight="16100" xr2:uid="{FF905779-AA47-4990-94FE-ABC250C14D95}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>sub-5008</t>
   </si>
@@ -69,9 +69,6 @@
     <t>sub-5058</t>
   </si>
   <si>
-    <t>sub-5069</t>
-  </si>
-  <si>
     <t>sub-5070</t>
   </si>
   <si>
@@ -144,15 +141,9 @@
     <t>sub-5031</t>
   </si>
   <si>
-    <t>sub-5567</t>
-  </si>
-  <si>
     <t>sub-5553</t>
   </si>
   <si>
-    <t>sub-5550</t>
-  </si>
-  <si>
     <t>sub-5543</t>
   </si>
   <si>
@@ -252,9 +243,6 @@
     <t>sub-5104</t>
   </si>
   <si>
-    <t>sub-5110</t>
-  </si>
-  <si>
     <t>sub-5137</t>
   </si>
   <si>
@@ -276,15 +264,9 @@
     <t>sub-5167</t>
   </si>
   <si>
-    <t>sub-5185</t>
-  </si>
-  <si>
     <t>sub-5186</t>
   </si>
   <si>
-    <t>sub-5194</t>
-  </si>
-  <si>
     <t>sub-5199</t>
   </si>
   <si>
@@ -318,9 +300,6 @@
     <t>sub-5304</t>
   </si>
   <si>
-    <t>sub-5307</t>
-  </si>
-  <si>
     <t>sub-5338</t>
   </si>
   <si>
@@ -331,9 +310,6 @@
   </si>
   <si>
     <t>sub-5374</t>
-  </si>
-  <si>
-    <t>sub-5378</t>
   </si>
   <si>
     <t>subjects</t>
@@ -688,22 +664,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78B551BD-8A51-487D-9B04-8F04A9206076}">
-  <dimension ref="A1:A101"/>
+  <dimension ref="A1:A93"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
@@ -728,7 +704,7 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
@@ -748,7 +724,7 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
@@ -758,17 +734,17 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
@@ -783,7 +759,7 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
@@ -793,7 +769,7 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
@@ -808,42 +784,42 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
@@ -853,347 +829,307 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>91</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
